--- a/02_指示書検証テスト/03_指示書テンプレート/01_指示書作成用(テスト).xlsx
+++ b/02_指示書検証テスト/03_指示書テンプレート/01_指示書作成用(テスト).xlsx
@@ -1,20 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\D2312\Desktop\指示書検証テスト\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\chito\coachtech\dispatch-automation-project\02_指示書検証テスト\03_指示書テンプレート\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B8AEA33-E2F3-4A83-803B-6CB5E587A031}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D0C761A-028D-4FD0-B81D-8DF05EE3EF73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7515" yWindow="2805" windowWidth="24180" windowHeight="13890" xr2:uid="{965BC491-ED8E-4E9B-9689-F27CD1BDBE26}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{965BC491-ED8E-4E9B-9689-F27CD1BDBE26}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$L$54</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -34,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="58">
   <si>
     <t>運送委託書　/　運送引取書</t>
   </si>
@@ -103,9 +106,6 @@
   </si>
   <si>
     <t>内容</t>
-  </si>
-  <si>
-    <t>雑貨</t>
   </si>
   <si>
     <t>積込作業の委託</t>
@@ -563,7 +563,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="138">
+  <cellXfs count="147">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -601,9 +601,6 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
     </xf>
@@ -631,12 +628,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -649,12 +640,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -673,10 +658,283 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -691,290 +949,59 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -994,9 +1021,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 テーマ">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1034,7 +1061,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1140,7 +1167,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1282,7 +1309,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1291,27 +1318,27 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD5669EE-9E78-4687-BF93-E0E6CAB4EAE3}">
   <dimension ref="A1:K54"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="9" max="11" width="9.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="128" t="s">
+    <row r="1" spans="1:11" ht="27.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1" s="33" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="128"/>
-      <c r="C1" s="128"/>
-      <c r="D1" s="128"/>
-      <c r="E1" s="128"/>
-      <c r="F1" s="128"/>
-      <c r="G1" s="128"/>
-      <c r="H1" s="128"/>
-      <c r="I1" s="128"/>
-      <c r="J1" s="128"/>
-      <c r="K1" s="128"/>
-    </row>
-    <row r="2" spans="1:11" ht="30.75" thickTop="1" x14ac:dyDescent="0.45">
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="33"/>
+      <c r="H1" s="33"/>
+      <c r="I1" s="33"/>
+      <c r="J1" s="33"/>
+      <c r="K1" s="33"/>
+    </row>
+    <row r="2" spans="1:11" ht="30.5" thickTop="1" x14ac:dyDescent="0.65">
       <c r="A2" s="1"/>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -1323,137 +1350,137 @@
       <c r="I2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="J2" s="129" t="s">
+      <c r="J2" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="K2" s="129"/>
-    </row>
-    <row r="3" spans="1:11" ht="19.5" x14ac:dyDescent="0.4">
-      <c r="A3" s="122" t="s">
+      <c r="K2" s="34"/>
+    </row>
+    <row r="3" spans="1:11" ht="19.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="125" t="s">
+      <c r="B3" s="38" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="130" t="s">
-        <v>57</v>
-      </c>
-      <c r="D3" s="131"/>
-      <c r="E3" s="131"/>
-      <c r="F3" s="131"/>
-      <c r="G3" s="131"/>
-      <c r="H3" s="132"/>
+      <c r="C3" s="40" t="s">
+        <v>56</v>
+      </c>
+      <c r="D3" s="41"/>
+      <c r="E3" s="41"/>
+      <c r="F3" s="41"/>
+      <c r="G3" s="41"/>
+      <c r="H3" s="42"/>
       <c r="I3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="J3" s="69" t="s">
-        <v>58</v>
-      </c>
-      <c r="K3" s="70"/>
-    </row>
-    <row r="4" spans="1:11" ht="19.5" x14ac:dyDescent="0.4">
-      <c r="A4" s="123"/>
-      <c r="B4" s="127"/>
-      <c r="C4" s="133"/>
-      <c r="D4" s="134"/>
-      <c r="E4" s="134"/>
-      <c r="F4" s="134"/>
-      <c r="G4" s="134"/>
-      <c r="H4" s="135"/>
+      <c r="J3" s="46" t="s">
+        <v>57</v>
+      </c>
+      <c r="K3" s="47"/>
+    </row>
+    <row r="4" spans="1:11" ht="19.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" s="36"/>
+      <c r="B4" s="39"/>
+      <c r="C4" s="43"/>
+      <c r="D4" s="44"/>
+      <c r="E4" s="44"/>
+      <c r="F4" s="44"/>
+      <c r="G4" s="44"/>
+      <c r="H4" s="45"/>
       <c r="I4" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="69" t="s">
-        <v>58</v>
-      </c>
-      <c r="K4" s="70"/>
-    </row>
-    <row r="5" spans="1:11" ht="19.5" x14ac:dyDescent="0.4">
-      <c r="A5" s="123"/>
-      <c r="B5" s="125" t="s">
+      <c r="J4" s="46" t="s">
+        <v>57</v>
+      </c>
+      <c r="K4" s="47"/>
+    </row>
+    <row r="5" spans="1:11" ht="19.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" s="36"/>
+      <c r="B5" s="38" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="74" t="s">
-        <v>57</v>
-      </c>
-      <c r="D5" s="136"/>
-      <c r="E5" s="136"/>
-      <c r="F5" s="136"/>
-      <c r="G5" s="136"/>
-      <c r="H5" s="75"/>
+      <c r="C5" s="48" t="s">
+        <v>56</v>
+      </c>
+      <c r="D5" s="49"/>
+      <c r="E5" s="49"/>
+      <c r="F5" s="49"/>
+      <c r="G5" s="49"/>
+      <c r="H5" s="50"/>
       <c r="I5" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="J5" s="69" t="s">
-        <v>58</v>
-      </c>
-      <c r="K5" s="70"/>
-    </row>
-    <row r="6" spans="1:11" ht="19.5" x14ac:dyDescent="0.4">
-      <c r="A6" s="124"/>
-      <c r="B6" s="127"/>
-      <c r="C6" s="76"/>
-      <c r="D6" s="137"/>
-      <c r="E6" s="137"/>
-      <c r="F6" s="137"/>
-      <c r="G6" s="137"/>
-      <c r="H6" s="77"/>
+      <c r="J5" s="46" t="s">
+        <v>57</v>
+      </c>
+      <c r="K5" s="47"/>
+    </row>
+    <row r="6" spans="1:11" ht="19.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="37"/>
+      <c r="B6" s="39"/>
+      <c r="C6" s="51"/>
+      <c r="D6" s="52"/>
+      <c r="E6" s="52"/>
+      <c r="F6" s="52"/>
+      <c r="G6" s="52"/>
+      <c r="H6" s="53"/>
       <c r="I6" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="J6" s="69" t="s">
-        <v>58</v>
-      </c>
-      <c r="K6" s="70"/>
-    </row>
-    <row r="7" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="122" t="s">
+      <c r="J6" s="46" t="s">
+        <v>57</v>
+      </c>
+      <c r="K6" s="47"/>
+    </row>
+    <row r="7" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" s="35" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="125" t="s">
+      <c r="B7" s="38" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="46"/>
-      <c r="D7" s="46"/>
-      <c r="E7" s="46"/>
-      <c r="F7" s="46"/>
-      <c r="G7" s="46"/>
-      <c r="H7" s="46" t="s">
+      <c r="C7" s="55"/>
+      <c r="D7" s="55"/>
+      <c r="E7" s="55"/>
+      <c r="F7" s="55"/>
+      <c r="G7" s="55"/>
+      <c r="H7" s="55" t="s">
         <v>11</v>
       </c>
-      <c r="I7" s="125" t="s">
+      <c r="I7" s="38" t="s">
         <v>5</v>
       </c>
-      <c r="J7" s="46"/>
-      <c r="K7" s="46"/>
-    </row>
-    <row r="8" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="123"/>
-      <c r="B8" s="126"/>
-      <c r="C8" s="46"/>
-      <c r="D8" s="46"/>
-      <c r="E8" s="46"/>
-      <c r="F8" s="46"/>
-      <c r="G8" s="46"/>
-      <c r="H8" s="46"/>
-      <c r="I8" s="126"/>
-      <c r="J8" s="46"/>
-      <c r="K8" s="46"/>
-    </row>
-    <row r="9" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="124"/>
-      <c r="B9" s="127"/>
-      <c r="C9" s="46"/>
-      <c r="D9" s="46"/>
-      <c r="E9" s="46"/>
-      <c r="F9" s="46"/>
-      <c r="G9" s="46"/>
-      <c r="H9" s="46"/>
-      <c r="I9" s="127"/>
-      <c r="J9" s="46"/>
-      <c r="K9" s="46"/>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="J7" s="55"/>
+      <c r="K7" s="55"/>
+    </row>
+    <row r="8" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" s="36"/>
+      <c r="B8" s="54"/>
+      <c r="C8" s="55"/>
+      <c r="D8" s="55"/>
+      <c r="E8" s="55"/>
+      <c r="F8" s="55"/>
+      <c r="G8" s="55"/>
+      <c r="H8" s="55"/>
+      <c r="I8" s="54"/>
+      <c r="J8" s="55"/>
+      <c r="K8" s="55"/>
+    </row>
+    <row r="9" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" s="37"/>
+      <c r="B9" s="39"/>
+      <c r="C9" s="55"/>
+      <c r="D9" s="55"/>
+      <c r="E9" s="55"/>
+      <c r="F9" s="55"/>
+      <c r="G9" s="55"/>
+      <c r="H9" s="55"/>
+      <c r="I9" s="39"/>
+      <c r="J9" s="55"/>
+      <c r="K9" s="55"/>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
@@ -1466,88 +1493,88 @@
       <c r="J10" s="1"/>
       <c r="K10" s="1"/>
     </row>
-    <row r="11" spans="1:11" ht="28.5" x14ac:dyDescent="0.4">
-      <c r="A11" s="116" t="s">
+    <row r="11" spans="1:11" ht="26.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" s="56" t="s">
         <v>12</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C11" s="103"/>
-      <c r="D11" s="104"/>
-      <c r="E11" s="104"/>
-      <c r="F11" s="105"/>
-      <c r="G11" s="69" t="s">
+      <c r="C11" s="59"/>
+      <c r="D11" s="60"/>
+      <c r="E11" s="60"/>
+      <c r="F11" s="61"/>
+      <c r="G11" s="46" t="s">
         <v>14</v>
       </c>
-      <c r="H11" s="106"/>
-      <c r="I11" s="104"/>
-      <c r="J11" s="104"/>
-      <c r="K11" s="104"/>
-    </row>
-    <row r="12" spans="1:11" ht="28.5" x14ac:dyDescent="0.4">
-      <c r="A12" s="117"/>
+      <c r="H11" s="62"/>
+      <c r="I11" s="60"/>
+      <c r="J11" s="60"/>
+      <c r="K11" s="60"/>
+    </row>
+    <row r="12" spans="1:11" ht="26.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" s="57"/>
       <c r="B12" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C12" s="108"/>
-      <c r="D12" s="109"/>
-      <c r="E12" s="109"/>
-      <c r="F12" s="109"/>
-      <c r="G12" s="109"/>
-      <c r="H12" s="109"/>
-      <c r="I12" s="109"/>
-      <c r="J12" s="109"/>
-      <c r="K12" s="109"/>
-    </row>
-    <row r="13" spans="1:11" ht="28.5" x14ac:dyDescent="0.4">
-      <c r="A13" s="117"/>
+      <c r="C12" s="63"/>
+      <c r="D12" s="64"/>
+      <c r="E12" s="64"/>
+      <c r="F12" s="64"/>
+      <c r="G12" s="64"/>
+      <c r="H12" s="64"/>
+      <c r="I12" s="64"/>
+      <c r="J12" s="64"/>
+      <c r="K12" s="64"/>
+    </row>
+    <row r="13" spans="1:11" ht="26.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" s="57"/>
       <c r="B13" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C13" s="111"/>
-      <c r="D13" s="112"/>
-      <c r="E13" s="112"/>
-      <c r="F13" s="112"/>
-      <c r="G13" s="112"/>
-      <c r="H13" s="112"/>
-      <c r="I13" s="112"/>
-      <c r="J13" s="112"/>
-      <c r="K13" s="112"/>
-    </row>
-    <row r="14" spans="1:11" ht="28.5" x14ac:dyDescent="0.4">
-      <c r="A14" s="117"/>
+      <c r="C13" s="65"/>
+      <c r="D13" s="66"/>
+      <c r="E13" s="66"/>
+      <c r="F13" s="66"/>
+      <c r="G13" s="66"/>
+      <c r="H13" s="66"/>
+      <c r="I13" s="66"/>
+      <c r="J13" s="66"/>
+      <c r="K13" s="66"/>
+    </row>
+    <row r="14" spans="1:11" ht="26.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" s="57"/>
       <c r="B14" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C14" s="103"/>
-      <c r="D14" s="104"/>
-      <c r="E14" s="104"/>
-      <c r="F14" s="105"/>
-      <c r="G14" s="69" t="s">
+      <c r="C14" s="59"/>
+      <c r="D14" s="60"/>
+      <c r="E14" s="60"/>
+      <c r="F14" s="61"/>
+      <c r="G14" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="H14" s="70"/>
-      <c r="I14" s="111"/>
-      <c r="J14" s="112"/>
-      <c r="K14" s="112"/>
-    </row>
-    <row r="15" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="118"/>
+      <c r="H14" s="47"/>
+      <c r="I14" s="65"/>
+      <c r="J14" s="66"/>
+      <c r="K14" s="66"/>
+    </row>
+    <row r="15" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" s="58"/>
       <c r="B15" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C15" s="119"/>
-      <c r="D15" s="120"/>
-      <c r="E15" s="120"/>
-      <c r="F15" s="120"/>
-      <c r="G15" s="120"/>
-      <c r="H15" s="120"/>
-      <c r="I15" s="120"/>
-      <c r="J15" s="120"/>
-      <c r="K15" s="121"/>
-    </row>
-    <row r="16" spans="1:11" ht="28.5" x14ac:dyDescent="0.4">
+      <c r="C15" s="67"/>
+      <c r="D15" s="68"/>
+      <c r="E15" s="68"/>
+      <c r="F15" s="68"/>
+      <c r="G15" s="68"/>
+      <c r="H15" s="68"/>
+      <c r="I15" s="68"/>
+      <c r="J15" s="68"/>
+      <c r="K15" s="69"/>
+    </row>
+    <row r="16" spans="1:11" ht="26.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="6"/>
       <c r="B16" s="6"/>
       <c r="C16" s="6"/>
@@ -1560,131 +1587,131 @@
       <c r="J16" s="6"/>
       <c r="K16" s="6"/>
     </row>
-    <row r="17" spans="1:11" ht="28.5" x14ac:dyDescent="0.4">
-      <c r="A17" s="100" t="s">
+    <row r="17" spans="1:11" ht="26.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" s="70" t="s">
         <v>18</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C17" s="103"/>
-      <c r="D17" s="104"/>
-      <c r="E17" s="104"/>
-      <c r="F17" s="105"/>
-      <c r="G17" s="69" t="s">
+      <c r="C17" s="59"/>
+      <c r="D17" s="60"/>
+      <c r="E17" s="60"/>
+      <c r="F17" s="61"/>
+      <c r="G17" s="46" t="s">
         <v>14</v>
       </c>
-      <c r="H17" s="106"/>
-      <c r="I17" s="107"/>
-      <c r="J17" s="107"/>
-      <c r="K17" s="107"/>
-    </row>
-    <row r="18" spans="1:11" ht="28.5" x14ac:dyDescent="0.4">
-      <c r="A18" s="101"/>
+      <c r="H17" s="62"/>
+      <c r="I17" s="73"/>
+      <c r="J17" s="73"/>
+      <c r="K17" s="73"/>
+    </row>
+    <row r="18" spans="1:11" ht="26.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" s="71"/>
       <c r="B18" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C18" s="108"/>
-      <c r="D18" s="109"/>
-      <c r="E18" s="109"/>
-      <c r="F18" s="109"/>
-      <c r="G18" s="109"/>
-      <c r="H18" s="109"/>
-      <c r="I18" s="109"/>
-      <c r="J18" s="109"/>
-      <c r="K18" s="110"/>
-    </row>
-    <row r="19" spans="1:11" ht="28.5" x14ac:dyDescent="0.4">
-      <c r="A19" s="101"/>
+      <c r="C18" s="63"/>
+      <c r="D18" s="64"/>
+      <c r="E18" s="64"/>
+      <c r="F18" s="64"/>
+      <c r="G18" s="64"/>
+      <c r="H18" s="64"/>
+      <c r="I18" s="64"/>
+      <c r="J18" s="64"/>
+      <c r="K18" s="74"/>
+    </row>
+    <row r="19" spans="1:11" ht="26.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A19" s="71"/>
       <c r="B19" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C19" s="108"/>
-      <c r="D19" s="109"/>
-      <c r="E19" s="109"/>
-      <c r="F19" s="109"/>
-      <c r="G19" s="109"/>
-      <c r="H19" s="109"/>
-      <c r="I19" s="109"/>
-      <c r="J19" s="109"/>
-      <c r="K19" s="110"/>
-    </row>
-    <row r="20" spans="1:11" ht="28.5" x14ac:dyDescent="0.4">
-      <c r="A20" s="101"/>
+      <c r="C19" s="63"/>
+      <c r="D19" s="64"/>
+      <c r="E19" s="64"/>
+      <c r="F19" s="64"/>
+      <c r="G19" s="64"/>
+      <c r="H19" s="64"/>
+      <c r="I19" s="64"/>
+      <c r="J19" s="64"/>
+      <c r="K19" s="74"/>
+    </row>
+    <row r="20" spans="1:11" ht="26.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A20" s="71"/>
       <c r="B20" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C20" s="103"/>
-      <c r="D20" s="104"/>
-      <c r="E20" s="104"/>
-      <c r="F20" s="105"/>
-      <c r="G20" s="69" t="s">
+      <c r="C20" s="59"/>
+      <c r="D20" s="60"/>
+      <c r="E20" s="60"/>
+      <c r="F20" s="61"/>
+      <c r="G20" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="H20" s="70"/>
-      <c r="I20" s="111"/>
-      <c r="J20" s="112"/>
-      <c r="K20" s="112"/>
-    </row>
-    <row r="21" spans="1:11" ht="28.5" x14ac:dyDescent="0.4">
-      <c r="A21" s="102"/>
+      <c r="H20" s="47"/>
+      <c r="I20" s="65"/>
+      <c r="J20" s="66"/>
+      <c r="K20" s="66"/>
+    </row>
+    <row r="21" spans="1:11" ht="26.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A21" s="72"/>
       <c r="B21" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="C21" s="113"/>
-      <c r="D21" s="114"/>
-      <c r="E21" s="114"/>
-      <c r="F21" s="114"/>
-      <c r="G21" s="114"/>
-      <c r="H21" s="114"/>
-      <c r="I21" s="114"/>
-      <c r="J21" s="114"/>
-      <c r="K21" s="115"/>
-    </row>
-    <row r="22" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="69" t="s">
+      <c r="C21" s="75"/>
+      <c r="D21" s="76"/>
+      <c r="E21" s="76"/>
+      <c r="F21" s="76"/>
+      <c r="G21" s="76"/>
+      <c r="H21" s="76"/>
+      <c r="I21" s="76"/>
+      <c r="J21" s="76"/>
+      <c r="K21" s="77"/>
+    </row>
+    <row r="22" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A22" s="46" t="s">
         <v>19</v>
       </c>
-      <c r="B22" s="70"/>
-      <c r="C22" s="71"/>
-      <c r="D22" s="72"/>
-      <c r="E22" s="72"/>
-      <c r="F22" s="72"/>
-      <c r="G22" s="72"/>
-      <c r="H22" s="72"/>
-      <c r="I22" s="72"/>
-      <c r="J22" s="72"/>
-      <c r="K22" s="73"/>
-    </row>
-    <row r="23" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="74" t="s">
+      <c r="B22" s="47"/>
+      <c r="C22" s="94"/>
+      <c r="D22" s="95"/>
+      <c r="E22" s="95"/>
+      <c r="F22" s="95"/>
+      <c r="G22" s="95"/>
+      <c r="H22" s="95"/>
+      <c r="I22" s="95"/>
+      <c r="J22" s="95"/>
+      <c r="K22" s="96"/>
+    </row>
+    <row r="23" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A23" s="48" t="s">
         <v>19</v>
       </c>
-      <c r="B23" s="75"/>
-      <c r="C23" s="78"/>
-      <c r="D23" s="79"/>
-      <c r="E23" s="79"/>
-      <c r="F23" s="79"/>
-      <c r="G23" s="79"/>
-      <c r="H23" s="79"/>
-      <c r="I23" s="79"/>
-      <c r="J23" s="79"/>
-      <c r="K23" s="80"/>
-    </row>
-    <row r="24" spans="1:11" ht="39" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="76"/>
-      <c r="B24" s="77"/>
-      <c r="C24" s="81"/>
-      <c r="D24" s="82"/>
-      <c r="E24" s="82"/>
-      <c r="F24" s="82"/>
-      <c r="G24" s="82"/>
-      <c r="H24" s="82"/>
-      <c r="I24" s="82"/>
-      <c r="J24" s="82"/>
-      <c r="K24" s="83"/>
-    </row>
-    <row r="25" spans="1:11" ht="21" x14ac:dyDescent="0.4">
+      <c r="B23" s="50"/>
+      <c r="C23" s="97"/>
+      <c r="D23" s="98"/>
+      <c r="E23" s="98"/>
+      <c r="F23" s="98"/>
+      <c r="G23" s="98"/>
+      <c r="H23" s="98"/>
+      <c r="I23" s="98"/>
+      <c r="J23" s="98"/>
+      <c r="K23" s="99"/>
+    </row>
+    <row r="24" spans="1:11" ht="39" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A24" s="51"/>
+      <c r="B24" s="53"/>
+      <c r="C24" s="100"/>
+      <c r="D24" s="101"/>
+      <c r="E24" s="101"/>
+      <c r="F24" s="101"/>
+      <c r="G24" s="101"/>
+      <c r="H24" s="101"/>
+      <c r="I24" s="101"/>
+      <c r="J24" s="101"/>
+      <c r="K24" s="102"/>
+    </row>
+    <row r="25" spans="1:11" ht="22" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="8"/>
       <c r="B25" s="9"/>
       <c r="C25" s="10"/>
@@ -1697,45 +1724,43 @@
       <c r="J25" s="10"/>
       <c r="K25" s="10"/>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A26" s="84" t="s">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A26" s="78" t="s">
         <v>20</v>
       </c>
-      <c r="B26" s="86"/>
-      <c r="C26" s="87"/>
-      <c r="D26" s="84" t="s">
+      <c r="B26" s="80"/>
+      <c r="C26" s="81"/>
+      <c r="D26" s="78" t="s">
         <v>21</v>
       </c>
-      <c r="E26" s="90"/>
-      <c r="F26" s="91"/>
-      <c r="G26" s="92"/>
+      <c r="E26" s="84"/>
+      <c r="F26" s="85"/>
+      <c r="G26" s="86"/>
       <c r="H26" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="I26" s="96" t="s">
-        <v>23</v>
-      </c>
-      <c r="J26" s="97"/>
-      <c r="K26" s="97"/>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A27" s="85"/>
-      <c r="B27" s="88"/>
-      <c r="C27" s="89"/>
-      <c r="D27" s="85"/>
-      <c r="E27" s="93"/>
-      <c r="F27" s="94"/>
-      <c r="G27" s="95"/>
+      <c r="I26" s="90"/>
+      <c r="J26" s="91"/>
+      <c r="K26" s="91"/>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A27" s="79"/>
+      <c r="B27" s="82"/>
+      <c r="C27" s="83"/>
+      <c r="D27" s="79"/>
+      <c r="E27" s="87"/>
+      <c r="F27" s="88"/>
+      <c r="G27" s="89"/>
       <c r="H27" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="I27" s="98"/>
-      <c r="J27" s="99"/>
-      <c r="K27" s="99"/>
-    </row>
-    <row r="28" spans="1:11" ht="21" x14ac:dyDescent="0.4">
-      <c r="A28" s="14"/>
-      <c r="B28" s="15"/>
+      <c r="I27" s="92"/>
+      <c r="J27" s="93"/>
+      <c r="K27" s="93"/>
+    </row>
+    <row r="28" spans="1:11" ht="22" x14ac:dyDescent="0.55000000000000004">
+      <c r="A28" s="13"/>
+      <c r="B28" s="14"/>
       <c r="C28" s="10"/>
       <c r="D28" s="10"/>
       <c r="E28" s="10"/>
@@ -1746,155 +1771,155 @@
       <c r="J28" s="10"/>
       <c r="K28" s="10"/>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A29" s="58" t="s">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A29" s="131" t="s">
+        <v>23</v>
+      </c>
+      <c r="B29" s="131"/>
+      <c r="C29" s="131" t="s">
         <v>24</v>
       </c>
-      <c r="B29" s="60"/>
-      <c r="C29" s="58" t="s">
+      <c r="D29" s="131"/>
+      <c r="E29" s="131" t="s">
         <v>25</v>
       </c>
-      <c r="D29" s="59"/>
-      <c r="E29" s="59" t="s">
+      <c r="F29" s="131"/>
+      <c r="G29" s="131"/>
+      <c r="H29" s="131"/>
+      <c r="I29" s="131" t="s">
         <v>26</v>
       </c>
-      <c r="F29" s="59"/>
-      <c r="G29" s="59"/>
-      <c r="H29" s="59"/>
-      <c r="I29" s="59" t="s">
+      <c r="J29" s="131"/>
+      <c r="K29" s="131"/>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A30" s="131" t="s">
         <v>27</v>
       </c>
-      <c r="J29" s="59"/>
-      <c r="K29" s="59"/>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A30" s="58" t="s">
-        <v>28</v>
-      </c>
-      <c r="B30" s="60"/>
-      <c r="C30" s="58" t="s">
+      <c r="B30" s="131"/>
+      <c r="C30" s="131" t="s">
+        <v>24</v>
+      </c>
+      <c r="D30" s="131"/>
+      <c r="E30" s="131" t="s">
         <v>25</v>
       </c>
-      <c r="D30" s="59"/>
-      <c r="E30" s="59" t="s">
+      <c r="F30" s="131"/>
+      <c r="G30" s="131"/>
+      <c r="H30" s="131"/>
+      <c r="I30" s="131" t="s">
         <v>26</v>
       </c>
-      <c r="F30" s="59"/>
-      <c r="G30" s="59"/>
-      <c r="H30" s="59"/>
-      <c r="I30" s="59" t="s">
-        <v>27</v>
-      </c>
-      <c r="J30" s="59"/>
-      <c r="K30" s="59"/>
-    </row>
-    <row r="31" spans="1:11" ht="33" x14ac:dyDescent="0.4">
+      <c r="J30" s="131"/>
+      <c r="K30" s="131"/>
+    </row>
+    <row r="31" spans="1:11" ht="32.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="5"/>
       <c r="B31" s="5"/>
-      <c r="C31" s="16"/>
-      <c r="D31" s="16"/>
-      <c r="E31" s="16"/>
-      <c r="F31" s="16"/>
-      <c r="G31" s="16"/>
-      <c r="H31" s="16"/>
-      <c r="I31" s="16"/>
-      <c r="J31" s="16"/>
-      <c r="K31" s="17"/>
-    </row>
-    <row r="32" spans="1:11" ht="19.5" x14ac:dyDescent="0.4">
-      <c r="A32" s="58" t="s">
+      <c r="C31" s="15"/>
+      <c r="D31" s="15"/>
+      <c r="E31" s="15"/>
+      <c r="F31" s="15"/>
+      <c r="G31" s="15"/>
+      <c r="H31" s="15"/>
+      <c r="I31" s="15"/>
+      <c r="J31" s="15"/>
+      <c r="K31" s="16"/>
+    </row>
+    <row r="32" spans="1:11" ht="19.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A32" s="103" t="s">
+        <v>28</v>
+      </c>
+      <c r="B32" s="104"/>
+      <c r="C32" s="106" t="s">
+        <v>55</v>
+      </c>
+      <c r="D32" s="107"/>
+      <c r="E32" s="107"/>
+      <c r="F32" s="108"/>
+      <c r="G32" s="103" t="s">
         <v>29</v>
       </c>
-      <c r="B32" s="60"/>
-      <c r="C32" s="64" t="s">
-        <v>56</v>
-      </c>
-      <c r="D32" s="65"/>
-      <c r="E32" s="65"/>
-      <c r="F32" s="66"/>
-      <c r="G32" s="58" t="s">
+      <c r="H32" s="104"/>
+      <c r="I32" s="103" t="s">
         <v>30</v>
       </c>
-      <c r="H32" s="60"/>
-      <c r="I32" s="58" t="s">
+      <c r="J32" s="105"/>
+      <c r="K32" s="104"/>
+    </row>
+    <row r="33" spans="1:11" ht="32.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A33" s="103" t="s">
         <v>31</v>
       </c>
-      <c r="J32" s="59"/>
-      <c r="K32" s="60"/>
-    </row>
-    <row r="33" spans="1:11" ht="33" x14ac:dyDescent="0.4">
-      <c r="A33" s="58" t="s">
+      <c r="B33" s="104"/>
+      <c r="C33" s="106" t="s">
         <v>32</v>
       </c>
-      <c r="B33" s="60"/>
-      <c r="C33" s="64" t="s">
+      <c r="D33" s="107"/>
+      <c r="E33" s="107"/>
+      <c r="F33" s="108"/>
+      <c r="G33" s="109"/>
+      <c r="H33" s="110"/>
+      <c r="I33" s="32"/>
+      <c r="J33" s="32"/>
+      <c r="K33" s="132"/>
+    </row>
+    <row r="34" spans="1:11" ht="19.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A34" s="103" t="s">
         <v>33</v>
       </c>
-      <c r="D33" s="65"/>
-      <c r="E33" s="65"/>
-      <c r="F33" s="66"/>
-      <c r="G33" s="67"/>
-      <c r="H33" s="68"/>
-      <c r="I33" s="16"/>
-      <c r="J33" s="16"/>
-      <c r="K33" s="16"/>
-    </row>
-    <row r="34" spans="1:11" ht="19.5" x14ac:dyDescent="0.4">
-      <c r="A34" s="58" t="s">
+      <c r="B34" s="104"/>
+      <c r="C34" s="106" t="s">
+        <v>32</v>
+      </c>
+      <c r="D34" s="107"/>
+      <c r="E34" s="107"/>
+      <c r="F34" s="108"/>
+      <c r="G34" s="103" t="s">
         <v>34</v>
       </c>
-      <c r="B34" s="60"/>
-      <c r="C34" s="64" t="s">
-        <v>33</v>
-      </c>
-      <c r="D34" s="65"/>
-      <c r="E34" s="65"/>
-      <c r="F34" s="66"/>
-      <c r="G34" s="58" t="s">
+      <c r="H34" s="105"/>
+      <c r="I34" s="105"/>
+      <c r="J34" s="105"/>
+      <c r="K34" s="104"/>
+    </row>
+    <row r="35" spans="1:11" ht="19.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A35" s="103" t="s">
         <v>35</v>
       </c>
-      <c r="H34" s="59"/>
-      <c r="I34" s="59"/>
-      <c r="J34" s="59"/>
-      <c r="K34" s="59"/>
-    </row>
-    <row r="35" spans="1:11" ht="19.5" x14ac:dyDescent="0.4">
-      <c r="A35" s="58" t="s">
+      <c r="B35" s="104"/>
+      <c r="C35" s="106" t="s">
+        <v>32</v>
+      </c>
+      <c r="D35" s="107"/>
+      <c r="E35" s="107"/>
+      <c r="F35" s="108"/>
+      <c r="G35" s="103" t="s">
         <v>36</v>
       </c>
-      <c r="B35" s="60"/>
-      <c r="C35" s="64" t="s">
-        <v>33</v>
-      </c>
-      <c r="D35" s="65"/>
-      <c r="E35" s="65"/>
-      <c r="F35" s="66"/>
-      <c r="G35" s="58" t="s">
+      <c r="H35" s="105"/>
+      <c r="I35" s="105"/>
+      <c r="J35" s="105"/>
+      <c r="K35" s="104"/>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A36" s="120" t="s">
         <v>37</v>
       </c>
-      <c r="H35" s="59"/>
-      <c r="I35" s="59"/>
-      <c r="J35" s="59"/>
-      <c r="K35" s="59"/>
-    </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A36" s="57" t="s">
-        <v>38</v>
-      </c>
-      <c r="B36" s="57"/>
-      <c r="C36" s="57"/>
-      <c r="D36" s="57"/>
-      <c r="E36" s="57"/>
-      <c r="F36" s="57"/>
-      <c r="G36" s="57"/>
-      <c r="H36" s="57"/>
-      <c r="I36" s="57"/>
-      <c r="J36" s="57"/>
-      <c r="K36" s="57"/>
-    </row>
-    <row r="37" spans="1:11" ht="21" x14ac:dyDescent="0.4">
-      <c r="A37" s="14"/>
-      <c r="B37" s="15"/>
+      <c r="B36" s="120"/>
+      <c r="C36" s="120"/>
+      <c r="D36" s="120"/>
+      <c r="E36" s="120"/>
+      <c r="F36" s="120"/>
+      <c r="G36" s="120"/>
+      <c r="H36" s="120"/>
+      <c r="I36" s="120"/>
+      <c r="J36" s="120"/>
+      <c r="K36" s="120"/>
+    </row>
+    <row r="37" spans="1:11" ht="22" x14ac:dyDescent="0.55000000000000004">
+      <c r="A37" s="13"/>
+      <c r="B37" s="14"/>
       <c r="C37" s="10"/>
       <c r="D37" s="10"/>
       <c r="E37" s="10"/>
@@ -1905,105 +1930,105 @@
       <c r="J37" s="10"/>
       <c r="K37" s="10"/>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A38" s="58" t="s">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A38" s="103" t="s">
+        <v>38</v>
+      </c>
+      <c r="B38" s="105"/>
+      <c r="C38" s="104"/>
+      <c r="D38" s="103" t="s">
         <v>39</v>
       </c>
-      <c r="B38" s="59"/>
-      <c r="C38" s="60"/>
-      <c r="D38" s="58" t="s">
+      <c r="E38" s="105"/>
+      <c r="F38" s="105"/>
+      <c r="G38" s="105"/>
+      <c r="H38" s="105"/>
+      <c r="I38" s="104"/>
+      <c r="J38" s="103" t="s">
         <v>40</v>
       </c>
-      <c r="E38" s="59"/>
-      <c r="F38" s="59"/>
-      <c r="G38" s="59"/>
-      <c r="H38" s="59"/>
-      <c r="I38" s="60"/>
-      <c r="J38" s="58" t="s">
+      <c r="K38" s="104"/>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A39" s="20"/>
+      <c r="B39" s="133"/>
+      <c r="C39" s="133"/>
+      <c r="D39" s="133"/>
+      <c r="E39" s="133"/>
+      <c r="F39" s="133"/>
+      <c r="G39" s="133"/>
+      <c r="H39" s="133"/>
+      <c r="I39" s="133"/>
+      <c r="J39" s="133"/>
+      <c r="K39" s="21"/>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A40" s="134" t="s">
         <v>41</v>
       </c>
-      <c r="K38" s="59"/>
-    </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A39" s="1"/>
-      <c r="B39" s="1"/>
-      <c r="C39" s="1"/>
-      <c r="D39" s="1"/>
-      <c r="E39" s="1"/>
-      <c r="F39" s="1"/>
-      <c r="G39" s="1"/>
-      <c r="H39" s="1"/>
-      <c r="I39" s="1"/>
-      <c r="J39" s="1"/>
-      <c r="K39" s="1"/>
-    </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A40" s="61" t="s">
+      <c r="B40" s="121"/>
+      <c r="C40" s="121"/>
+      <c r="D40" s="121"/>
+      <c r="E40" s="121"/>
+      <c r="F40" s="121"/>
+      <c r="G40" s="121"/>
+      <c r="H40" s="121"/>
+      <c r="I40" s="121"/>
+      <c r="J40" s="121"/>
+      <c r="K40" s="135"/>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A41" s="122" t="s">
         <v>42</v>
       </c>
-      <c r="B40" s="61"/>
-      <c r="C40" s="61"/>
-      <c r="D40" s="61"/>
-      <c r="E40" s="61"/>
-      <c r="F40" s="61"/>
-      <c r="G40" s="61"/>
-      <c r="H40" s="61"/>
-      <c r="I40" s="61"/>
-      <c r="J40" s="61"/>
-      <c r="K40" s="61"/>
-    </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A41" s="62" t="s">
+      <c r="B41" s="123"/>
+      <c r="C41" s="123"/>
+      <c r="D41" s="123"/>
+      <c r="E41" s="123"/>
+      <c r="F41" s="123"/>
+      <c r="G41" s="123"/>
+      <c r="H41" s="123"/>
+      <c r="I41" s="123"/>
+      <c r="J41" s="123"/>
+      <c r="K41" s="123"/>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A42" s="111" t="s">
         <v>43</v>
       </c>
-      <c r="B41" s="63"/>
-      <c r="C41" s="63"/>
-      <c r="D41" s="63"/>
-      <c r="E41" s="63"/>
-      <c r="F41" s="63"/>
-      <c r="G41" s="63"/>
-      <c r="H41" s="63"/>
-      <c r="I41" s="63"/>
-      <c r="J41" s="63"/>
-      <c r="K41" s="63"/>
-    </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A42" s="47" t="s">
+      <c r="B42" s="112"/>
+      <c r="C42" s="113"/>
+      <c r="D42" s="118" t="s">
+        <v>20</v>
+      </c>
+      <c r="E42" s="119"/>
+      <c r="F42" s="111" t="s">
         <v>44</v>
       </c>
-      <c r="B42" s="48"/>
-      <c r="C42" s="49"/>
-      <c r="D42" s="50" t="s">
-        <v>20</v>
-      </c>
-      <c r="E42" s="51"/>
-      <c r="F42" s="47" t="s">
+      <c r="G42" s="113"/>
+      <c r="H42" s="111" t="s">
         <v>45</v>
       </c>
-      <c r="G42" s="49"/>
-      <c r="H42" s="47" t="s">
+      <c r="I42" s="113"/>
+      <c r="J42" s="111" t="s">
         <v>46</v>
       </c>
-      <c r="I42" s="49"/>
-      <c r="J42" s="47" t="s">
-        <v>47</v>
-      </c>
-      <c r="K42" s="49"/>
-    </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A43" s="47"/>
-      <c r="B43" s="48"/>
-      <c r="C43" s="49"/>
-      <c r="D43" s="52"/>
-      <c r="E43" s="53"/>
-      <c r="F43" s="47"/>
-      <c r="G43" s="49"/>
-      <c r="H43" s="54"/>
-      <c r="I43" s="55"/>
-      <c r="J43" s="54"/>
-      <c r="K43" s="56"/>
-    </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="K42" s="113"/>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A43" s="111"/>
+      <c r="B43" s="112"/>
+      <c r="C43" s="113"/>
+      <c r="D43" s="114"/>
+      <c r="E43" s="115"/>
+      <c r="F43" s="111"/>
+      <c r="G43" s="113"/>
+      <c r="H43" s="116"/>
+      <c r="I43" s="117"/>
+      <c r="J43" s="116"/>
+      <c r="K43" s="117"/>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" s="1"/>
       <c r="B44" s="1"/>
       <c r="C44" s="1"/>
@@ -2016,222 +2041,159 @@
       <c r="J44" s="1"/>
       <c r="K44" s="1"/>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A45" s="18" t="s">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A45" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="B45" s="18"/>
+      <c r="C45" s="18"/>
+      <c r="D45" s="18"/>
+      <c r="E45" s="18"/>
+      <c r="F45" s="18"/>
+      <c r="G45" s="18"/>
+      <c r="H45" s="18"/>
+      <c r="I45" s="18"/>
+      <c r="J45" s="18"/>
+      <c r="K45" s="19"/>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A46" s="20"/>
+      <c r="B46" s="133"/>
+      <c r="C46" s="133"/>
+      <c r="D46" s="133"/>
+      <c r="E46" s="133"/>
+      <c r="F46" s="133"/>
+      <c r="G46" s="133"/>
+      <c r="H46" s="133"/>
+      <c r="I46" s="133"/>
+      <c r="J46" s="133"/>
+      <c r="K46" s="21"/>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A47" s="124" t="s">
         <v>48</v>
       </c>
-      <c r="B45" s="19"/>
-      <c r="C45" s="19"/>
-      <c r="D45" s="19"/>
-      <c r="E45" s="19"/>
-      <c r="F45" s="19"/>
-      <c r="G45" s="19"/>
-      <c r="H45" s="19"/>
-      <c r="I45" s="19"/>
-      <c r="J45" s="19"/>
-      <c r="K45" s="20"/>
-    </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A46" s="21"/>
-      <c r="B46" s="1"/>
-      <c r="C46" s="1"/>
-      <c r="D46" s="1"/>
-      <c r="E46" s="1"/>
-      <c r="F46" s="1"/>
-      <c r="G46" s="1"/>
-      <c r="H46" s="1"/>
-      <c r="I46" s="1"/>
-      <c r="J46" s="1"/>
-      <c r="K46" s="22"/>
-    </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A47" s="37" t="s">
+      <c r="B47" s="136"/>
+      <c r="C47" s="125"/>
+      <c r="D47" s="126" t="s">
         <v>49</v>
       </c>
-      <c r="B47" s="38"/>
-      <c r="C47" s="39"/>
-      <c r="D47" s="40" t="s">
+      <c r="E47" s="127"/>
+      <c r="F47" s="137" t="s">
         <v>50</v>
       </c>
-      <c r="E47" s="41"/>
-      <c r="F47" s="13" t="s">
+      <c r="G47" s="137"/>
+      <c r="H47" s="133"/>
+      <c r="I47" s="133"/>
+      <c r="J47" s="133"/>
+      <c r="K47" s="21"/>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A48" s="128" t="s">
         <v>51</v>
       </c>
-      <c r="G47" s="13"/>
-      <c r="H47" s="1"/>
-      <c r="I47" s="1"/>
-      <c r="J47" s="1"/>
-      <c r="K47" s="22"/>
-    </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A48" s="42" t="s">
+      <c r="B48" s="138"/>
+      <c r="C48" s="138"/>
+      <c r="D48" s="138"/>
+      <c r="E48" s="138"/>
+      <c r="F48" s="138"/>
+      <c r="G48" s="138"/>
+      <c r="H48" s="138"/>
+      <c r="I48" s="138"/>
+      <c r="J48" s="138"/>
+      <c r="K48" s="139"/>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A49" s="22"/>
+      <c r="B49" s="23"/>
+      <c r="C49" s="23"/>
+      <c r="D49" s="23"/>
+      <c r="E49" s="23"/>
+      <c r="F49" s="23"/>
+      <c r="G49" s="23"/>
+      <c r="H49" s="23"/>
+      <c r="I49" s="23"/>
+      <c r="J49" s="23"/>
+      <c r="K49" s="24"/>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A50" s="140"/>
+      <c r="B50" s="141"/>
+      <c r="C50" s="141"/>
+      <c r="D50" s="142"/>
+      <c r="E50" s="142"/>
+      <c r="F50" s="143"/>
+      <c r="G50" s="143"/>
+      <c r="H50" s="18"/>
+      <c r="I50" s="18"/>
+      <c r="J50" s="18"/>
+      <c r="K50" s="19"/>
+    </row>
+    <row r="51" spans="1:11" ht="32.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A51" s="25" t="s">
         <v>52</v>
       </c>
-      <c r="B48" s="43"/>
-      <c r="C48" s="43"/>
-      <c r="D48" s="43"/>
-      <c r="E48" s="43"/>
-      <c r="F48" s="43"/>
-      <c r="G48" s="43"/>
-      <c r="H48" s="43"/>
-      <c r="I48" s="43"/>
-      <c r="J48" s="43"/>
-      <c r="K48" s="43"/>
-    </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A49" s="25"/>
-      <c r="B49" s="26"/>
-      <c r="C49" s="26"/>
-      <c r="D49" s="26"/>
-      <c r="E49" s="26"/>
-      <c r="F49" s="26"/>
-      <c r="G49" s="26"/>
-      <c r="H49" s="26"/>
-      <c r="I49" s="26"/>
-      <c r="J49" s="26"/>
-      <c r="K49" s="27"/>
-    </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A50" s="23"/>
-      <c r="B50" s="15"/>
-      <c r="C50" s="15"/>
-      <c r="D50" s="24"/>
-      <c r="E50" s="24"/>
-      <c r="F50" s="13"/>
-      <c r="G50" s="13"/>
-      <c r="H50" s="1"/>
-      <c r="I50" s="1"/>
-      <c r="J50" s="1"/>
-      <c r="K50" s="22"/>
-    </row>
-    <row r="51" spans="1:11" ht="33" x14ac:dyDescent="0.4">
-      <c r="A51" s="28" t="s">
+      <c r="B51" s="144"/>
+      <c r="C51" s="145"/>
+      <c r="D51" s="145"/>
+      <c r="E51" s="145"/>
+      <c r="F51" s="145"/>
+      <c r="G51" s="145"/>
+      <c r="H51" s="145"/>
+      <c r="I51" s="145"/>
+      <c r="J51" s="133"/>
+      <c r="K51" s="21"/>
+    </row>
+    <row r="52" spans="1:11" ht="32.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A52" s="26"/>
+      <c r="B52" s="146" t="s">
         <v>53</v>
       </c>
-      <c r="B51" s="30"/>
-      <c r="C51" s="16"/>
-      <c r="D51" s="16"/>
-      <c r="E51" s="16"/>
-      <c r="F51" s="16"/>
-      <c r="G51" s="16"/>
-      <c r="H51" s="16"/>
-      <c r="I51" s="16"/>
-      <c r="J51" s="1"/>
-      <c r="K51" s="22"/>
-    </row>
-    <row r="52" spans="1:11" ht="33" x14ac:dyDescent="0.4">
-      <c r="A52" s="31"/>
-      <c r="B52" s="29" t="s">
+      <c r="C52" s="145"/>
+      <c r="D52" s="145"/>
+      <c r="E52" s="145"/>
+      <c r="F52" s="145"/>
+      <c r="G52" s="145"/>
+      <c r="H52" s="145"/>
+      <c r="I52" s="145"/>
+      <c r="J52" s="133"/>
+      <c r="K52" s="21"/>
+    </row>
+    <row r="53" spans="1:11" ht="25" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A53" s="26"/>
+      <c r="B53" s="129" t="s">
         <v>54</v>
       </c>
-      <c r="C52" s="16"/>
-      <c r="D52" s="16"/>
-      <c r="E52" s="16"/>
-      <c r="F52" s="16"/>
-      <c r="G52" s="16"/>
-      <c r="H52" s="16"/>
-      <c r="I52" s="16"/>
-      <c r="J52" s="1"/>
-      <c r="K52" s="22"/>
-    </row>
-    <row r="53" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A53" s="31"/>
-      <c r="B53" s="44" t="s">
-        <v>55</v>
-      </c>
-      <c r="C53" s="44"/>
-      <c r="D53" s="44"/>
-      <c r="E53" s="44"/>
-      <c r="F53" s="44"/>
-      <c r="G53" s="44"/>
-      <c r="H53" s="45"/>
-      <c r="I53" s="45"/>
-      <c r="J53" s="32"/>
-      <c r="K53" s="22"/>
-    </row>
-    <row r="54" spans="1:11" ht="19.5" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A54" s="33"/>
-      <c r="B54" s="34"/>
-      <c r="C54" s="34"/>
-      <c r="D54" s="35"/>
-      <c r="E54" s="35"/>
-      <c r="F54" s="36"/>
-      <c r="G54" s="36"/>
-      <c r="H54" s="26"/>
-      <c r="I54" s="26"/>
-      <c r="J54" s="26"/>
-      <c r="K54" s="27"/>
+      <c r="C53" s="129"/>
+      <c r="D53" s="129"/>
+      <c r="E53" s="129"/>
+      <c r="F53" s="129"/>
+      <c r="G53" s="129"/>
+      <c r="H53" s="130"/>
+      <c r="I53" s="130"/>
+      <c r="J53" s="27"/>
+      <c r="K53" s="21"/>
+    </row>
+    <row r="54" spans="1:11" ht="18.5" thickTop="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A54" s="28"/>
+      <c r="B54" s="29"/>
+      <c r="C54" s="29"/>
+      <c r="D54" s="30"/>
+      <c r="E54" s="30"/>
+      <c r="F54" s="31"/>
+      <c r="G54" s="31"/>
+      <c r="H54" s="23"/>
+      <c r="I54" s="23"/>
+      <c r="J54" s="23"/>
+      <c r="K54" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="89">
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="J2:K2"/>
-    <mergeCell ref="A3:A6"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C3:H4"/>
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="C5:H6"/>
-    <mergeCell ref="J5:K5"/>
-    <mergeCell ref="J6:K6"/>
-    <mergeCell ref="A7:A9"/>
-    <mergeCell ref="B7:B9"/>
-    <mergeCell ref="C7:G9"/>
-    <mergeCell ref="H7:H9"/>
-    <mergeCell ref="I7:I9"/>
-    <mergeCell ref="A11:A15"/>
-    <mergeCell ref="C11:F11"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="I11:K11"/>
-    <mergeCell ref="C12:K12"/>
-    <mergeCell ref="C13:K13"/>
-    <mergeCell ref="C14:F14"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="I14:K14"/>
-    <mergeCell ref="C15:K15"/>
-    <mergeCell ref="A17:A21"/>
-    <mergeCell ref="C17:F17"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="I17:K17"/>
-    <mergeCell ref="C18:K18"/>
-    <mergeCell ref="C19:K19"/>
-    <mergeCell ref="C20:F20"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="I20:K20"/>
-    <mergeCell ref="C21:K21"/>
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="B26:C27"/>
-    <mergeCell ref="D26:D27"/>
-    <mergeCell ref="E26:G27"/>
-    <mergeCell ref="I26:K27"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:K22"/>
-    <mergeCell ref="A23:B24"/>
-    <mergeCell ref="C23:K23"/>
-    <mergeCell ref="C24:K24"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="E29:H29"/>
-    <mergeCell ref="I29:K29"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="E30:H30"/>
-    <mergeCell ref="I30:K30"/>
-    <mergeCell ref="C35:F35"/>
-    <mergeCell ref="G35:K35"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="C32:F32"/>
-    <mergeCell ref="G32:H32"/>
-    <mergeCell ref="I32:K32"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="C33:F33"/>
-    <mergeCell ref="G33:H33"/>
-    <mergeCell ref="A43:C43"/>
-    <mergeCell ref="D43:E43"/>
-    <mergeCell ref="F43:G43"/>
-    <mergeCell ref="H43:I43"/>
-    <mergeCell ref="J43:K43"/>
+    <mergeCell ref="A47:C47"/>
+    <mergeCell ref="D47:E47"/>
+    <mergeCell ref="A48:K48"/>
+    <mergeCell ref="B53:G53"/>
+    <mergeCell ref="H53:I53"/>
     <mergeCell ref="J7:K9"/>
     <mergeCell ref="A42:C42"/>
     <mergeCell ref="D42:E42"/>
@@ -2248,11 +2210,74 @@
     <mergeCell ref="C34:F34"/>
     <mergeCell ref="G34:K34"/>
     <mergeCell ref="A35:B35"/>
-    <mergeCell ref="A47:C47"/>
-    <mergeCell ref="D47:E47"/>
-    <mergeCell ref="A48:K48"/>
-    <mergeCell ref="B53:G53"/>
-    <mergeCell ref="H53:I53"/>
+    <mergeCell ref="A43:C43"/>
+    <mergeCell ref="D43:E43"/>
+    <mergeCell ref="F43:G43"/>
+    <mergeCell ref="H43:I43"/>
+    <mergeCell ref="J43:K43"/>
+    <mergeCell ref="C35:F35"/>
+    <mergeCell ref="G35:K35"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="C32:F32"/>
+    <mergeCell ref="G32:H32"/>
+    <mergeCell ref="I32:K32"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="C33:F33"/>
+    <mergeCell ref="G33:H33"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="E29:H29"/>
+    <mergeCell ref="I29:K29"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="E30:H30"/>
+    <mergeCell ref="I30:K30"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:K22"/>
+    <mergeCell ref="A23:B24"/>
+    <mergeCell ref="C23:K23"/>
+    <mergeCell ref="C24:K24"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="B26:C27"/>
+    <mergeCell ref="D26:D27"/>
+    <mergeCell ref="E26:G27"/>
+    <mergeCell ref="I26:K27"/>
+    <mergeCell ref="A17:A21"/>
+    <mergeCell ref="C17:F17"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="I17:K17"/>
+    <mergeCell ref="C18:K18"/>
+    <mergeCell ref="C19:K19"/>
+    <mergeCell ref="C20:F20"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="I20:K20"/>
+    <mergeCell ref="C21:K21"/>
+    <mergeCell ref="A11:A15"/>
+    <mergeCell ref="C11:F11"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="I11:K11"/>
+    <mergeCell ref="C12:K12"/>
+    <mergeCell ref="C13:K13"/>
+    <mergeCell ref="C14:F14"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="I14:K14"/>
+    <mergeCell ref="C15:K15"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="B7:B9"/>
+    <mergeCell ref="C7:G9"/>
+    <mergeCell ref="H7:H9"/>
+    <mergeCell ref="I7:I9"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="A3:A6"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:H4"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="C5:H6"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="J6:K6"/>
   </mergeCells>
   <phoneticPr fontId="14"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
